--- a/public/templates/template-upload-plta.xlsx
+++ b/public/templates/template-upload-plta.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETUNJUK" sheetId="1" r:id="R1d4de8b0018b4063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ELEVATION_VOLUME" sheetId="2" r:id="R467df8555f0b47ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTOW" sheetId="3" r:id="Rd393228b096f4b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PETUNJUK" sheetId="1" r:id="R2d79efda2fa04bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ELEVATION_VOLUME" sheetId="2" r:id="R42fc7731cf3c4198"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,7 +509,7 @@
     </x:row>
     <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Satu workbook untuk seluruh PLTA. Jangan mengubah nama sheet atau nama kolom.</x:v>
+        <x:v>Satu workbook untuk kurva elevasi dan volume waduk. File dikirim langsung ke server tanpa parsing di browser.</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
         <x:v>Satu workbook untuk seluruh PLTA. Jangan mengubah nama sheet atau nama kolom.</x:v>
@@ -590,7 +589,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Area wajib untuk PLTA yang memilikinya. Untuk Wonogiri boleh kosong atau 0.</x:v>
+        <x:v>Area opsional. Jika kosong, backend akan menyimpannya sebagai 0.</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -598,12 +597,8 @@
       <x:c r="F8" s="14"/>
     </x:row>
     <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A9" s="14" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B9" s="14" t="str">
-        <x:v>RTOW wajib memakai tanggal valid berformat YYYY-MM-DD.</x:v>
-      </x:c>
+      <x:c r="A9" s="14"/>
+      <x:c r="B9" s="14"/>
       <x:c r="C9" s="14"/>
       <x:c r="D9" s="14"/>
       <x:c r="E9" s="14"/>
@@ -711,49 +706,25 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="21" t="str">
-        <x:v>RTOW</x:v>
-      </x:c>
-      <x:c r="B16" s="21" t="str">
-        <x:v>tanggal</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="str">
-        <x:v>Tanggal ISO</x:v>
-      </x:c>
-      <x:c r="D16" s="21" t="str">
-        <x:v>Ya</x:v>
-      </x:c>
-      <x:c r="E16" s="21" t="str">
-        <x:v>entries[].tanggal</x:v>
-      </x:c>
-      <x:c r="F16" s="21" t="str">
-        <x:v>2026-01-01</x:v>
-      </x:c>
+      <x:c r="A16" s="21"/>
+      <x:c r="B16" s="21"/>
+      <x:c r="C16" s="21"/>
+      <x:c r="D16" s="21"/>
+      <x:c r="E16" s="21"/>
+      <x:c r="F16" s="21"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="21" t="str">
-        <x:v>RTOW</x:v>
-      </x:c>
-      <x:c r="B17" s="21" t="str">
-        <x:v>target_elevasi</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="str">
-        <x:v>Angka</x:v>
-      </x:c>
-      <x:c r="D17" s="21" t="str">
-        <x:v>Ya</x:v>
-      </x:c>
-      <x:c r="E17" s="21" t="str">
-        <x:v>entries[].target_elevasi</x:v>
-      </x:c>
-      <x:c r="F17" s="21" t="n">
-        <x:v>228.5</x:v>
-      </x:c>
+      <x:c r="A17" s="21"/>
+      <x:c r="B17" s="21"/>
+      <x:c r="C17" s="21"/>
+      <x:c r="D17" s="21"/>
+      <x:c r="E17" s="21"/>
+      <x:c r="F17" s="21"/>
     </x:row>
     <x:row r="18"/>
     <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A19" s="28" t="str">
-        <x:v>Catatan: min_elevation dan max_elevation dihitung otomatis dari kolom elevation saat upload.</x:v>
+        <x:v>Catatan: year, min_elevation, dan max_elevation diproses oleh backend saat upload.</x:v>
       </x:c>
       <x:c r="B19" s="29" t="str">
         <x:v>Catatan: min_elevation dan max_elevation dihitung otomatis dari kolom elevation saat upload.</x:v>
@@ -932,122 +903,4 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>UPLOAD RTOW</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>UPLOAD RTOW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="33" t="str">
-        <x:v>Gunakan satu baris per tanggal. Tanggal harus valid dan berada pada tahun di sel B3.</x:v>
-      </x:c>
-      <x:c r="B2" s="33" t="str">
-        <x:v>Gunakan satu baris per tanggal. Tanggal harus valid dan berada pada tahun di sel B3.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="36" t="str">
-        <x:v>tahun</x:v>
-      </x:c>
-      <x:c r="B3" s="43" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="26" customHeight="1">
-      <x:c r="A5" s="19" t="str">
-        <x:v>tanggal</x:v>
-      </x:c>
-      <x:c r="B5" s="19" t="str">
-        <x:v>target_elevasi</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="45"/>
-      <x:c r="B6" s="44"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="45"/>
-      <x:c r="B7" s="44"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="45"/>
-      <x:c r="B8" s="44"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="45"/>
-      <x:c r="B9" s="44"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="45"/>
-      <x:c r="B10" s="44"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="45"/>
-      <x:c r="B11" s="44"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="45"/>
-      <x:c r="B12" s="44"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="45"/>
-      <x:c r="B13" s="44"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="45"/>
-      <x:c r="B14" s="44"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="45"/>
-      <x:c r="B15" s="44"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="45"/>
-      <x:c r="B16" s="44"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="45"/>
-      <x:c r="B17" s="44"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="45"/>
-      <x:c r="B18" s="44"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="45"/>
-      <x:c r="B19" s="44"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="45"/>
-      <x:c r="B20" s="44"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:B1"/>
-    <x:mergeCell ref="A2:B2"/>
-  </x:mergeCells>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="B3">
-      <x:formula1>1900</x:formula1>
-      <x:formula2>2100</x:formula2>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="B6:B380">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>